--- a/artfynd/A 59095-2024 artfynd.xlsx
+++ b/artfynd/A 59095-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106232271</v>
+        <v>106232227</v>
       </c>
       <c r="B2" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>365606.2014870174</v>
+        <v>365385</v>
       </c>
       <c r="R2" t="n">
-        <v>6641461.937393475</v>
+        <v>6641490</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,19 +747,9 @@
           <t>2022-11-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106232274</v>
+        <v>106232251</v>
       </c>
       <c r="B3" t="n">
-        <v>78614</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229504</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>365606.2014870174</v>
+        <v>365504</v>
       </c>
       <c r="R3" t="n">
-        <v>6641461.937393475</v>
+        <v>6641449</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,19 +848,9 @@
           <t>2022-11-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,12 +881,7 @@
         <v>106232273</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -950,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>365606.2014870174</v>
+        <v>365606</v>
       </c>
       <c r="R4" t="n">
-        <v>6641461.937393475</v>
+        <v>6641461</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,19 +949,9 @@
           <t>2022-11-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,6 +976,545 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>106232271</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nolby, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>365606</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6641461</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>106232253</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nolby, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>365504</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6641449</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>106232248</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nolby, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>365504</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6641449</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Slutade räkna vid 100 men det fanns fler.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113460444</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nolby, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>365504</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6641450</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>S-Arv-0832</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-07-04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-07-04</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>106232274</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80477</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>229504</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grynig filtlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Peltigera collina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nolby, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>365606</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6641461</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gunnarskog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-11-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
